--- a/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
+++ b/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SIHJU\Documents\PROGRAMACION\Analisis y desarrollo de software_tecnologo\Grupo 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccifu\OneDrive\Escritorio\AXXION_SYSTEM\_docs\trim_03\Normalización Modelo Relacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1940873-3F1C-4D6C-AECF-88F2C6CCEB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB465C5D-3106-427A-B34E-1FAA9117AC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F9FFE5D-8DC2-4520-A7DA-75C0721EFB2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4F9FFE5D-8DC2-4520-A7DA-75C0721EFB2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -567,10 +567,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -907,37 +911,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D31449-B9E3-460C-85DA-C946E15A5F7C}">
   <dimension ref="C3:L88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" s="30" t="s">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C3" s="28" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="30"/>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="28"/>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="3:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
@@ -951,7 +956,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="3:12" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C11" s="4" t="s">
         <v>0</v>
       </c>
@@ -983,7 +988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="3:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C12" s="7">
         <v>101</v>
       </c>
@@ -1015,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="3:12" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C13" s="7">
         <v>102</v>
       </c>
@@ -1047,7 +1052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="3:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:12" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="12">
         <v>103</v>
       </c>
@@ -1079,27 +1084,27 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C20" s="30" t="s">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C20" s="28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C24" s="30" t="s">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C24" s="28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="3:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
         <v>46</v>
       </c>
@@ -1107,7 +1112,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="3:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C28" s="2" t="s">
         <v>24</v>
       </c>
@@ -1121,7 +1126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="3:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C29" s="2">
         <v>1</v>
       </c>
@@ -1135,7 +1140,7 @@
         <v>55511223344</v>
       </c>
     </row>
-    <row r="30" spans="3:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C30" s="2">
         <v>2</v>
       </c>
@@ -1149,7 +1154,7 @@
         <v>55511223345</v>
       </c>
     </row>
-    <row r="31" spans="3:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C31" s="2">
         <v>2</v>
       </c>
@@ -1163,7 +1168,7 @@
         <v>5588776655</v>
       </c>
     </row>
-    <row r="33" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1" t="s">
         <v>54</v>
       </c>
@@ -1175,7 +1180,7 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="17" t="s">
         <v>34</v>
       </c>
@@ -1193,7 +1198,7 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C35" s="20">
         <v>51</v>
       </c>
@@ -1211,7 +1216,7 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C36" s="22">
         <v>52</v>
       </c>
@@ -1229,7 +1234,7 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1239,7 +1244,7 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C38" s="1" t="s">
         <v>55</v>
       </c>
@@ -1251,7 +1256,7 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C39" s="2" t="s">
         <v>44</v>
       </c>
@@ -1269,7 +1274,7 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C40" s="2">
         <v>901</v>
       </c>
@@ -1287,7 +1292,7 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C41" s="2">
         <v>902</v>
       </c>
@@ -1305,7 +1310,7 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C42" s="2">
         <v>903</v>
       </c>
@@ -1323,7 +1328,7 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -1333,7 +1338,7 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="1" t="s">
         <v>56</v>
       </c>
@@ -1345,7 +1350,7 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C45" s="17" t="s">
         <v>25</v>
       </c>
@@ -1357,7 +1362,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C46" s="20">
         <v>101</v>
       </c>
@@ -1381,7 +1386,7 @@
       </c>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C47" s="20">
         <v>102</v>
       </c>
@@ -1405,7 +1410,7 @@
       </c>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="3:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="22">
         <v>103</v>
       </c>
@@ -1429,7 +1434,7 @@
       </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1439,7 +1444,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -1449,7 +1454,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1459,30 +1464,30 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C52" s="30" t="s">
+    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C52" s="28" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C55" s="30"/>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C56" s="30" t="s">
+    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C55" s="28"/>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C56" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C59" s="1" t="s">
         <v>46</v>
       </c>
@@ -1490,7 +1495,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C60" s="2" t="s">
         <v>24</v>
       </c>
@@ -1504,7 +1509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C61" s="2">
         <v>1</v>
       </c>
@@ -1518,7 +1523,7 @@
         <v>55511223344</v>
       </c>
     </row>
-    <row r="62" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C62" s="2">
         <v>2</v>
       </c>
@@ -1532,7 +1537,7 @@
         <v>55511223345</v>
       </c>
     </row>
-    <row r="63" spans="3:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C63" s="2">
         <v>2</v>
       </c>
@@ -1546,7 +1551,7 @@
         <v>5588776655</v>
       </c>
     </row>
-    <row r="65" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="1" t="s">
         <v>54</v>
       </c>
@@ -1557,7 +1562,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C66" s="17" t="s">
         <v>34</v>
       </c>
@@ -1574,7 +1579,7 @@
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C67" s="20">
         <v>51</v>
       </c>
@@ -1591,7 +1596,7 @@
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C68" s="22">
         <v>52</v>
       </c>
@@ -1608,7 +1613,7 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -1617,7 +1622,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
         <v>55</v>
       </c>
@@ -1628,7 +1633,7 @@
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C71" s="2" t="s">
         <v>44</v>
       </c>
@@ -1645,7 +1650,7 @@
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C72" s="2">
         <v>901</v>
       </c>
@@ -1662,7 +1667,7 @@
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C73" s="2">
         <v>902</v>
       </c>
@@ -1679,7 +1684,7 @@
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C74" s="2">
         <v>903</v>
       </c>
@@ -1696,7 +1701,7 @@
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -1705,54 +1710,50 @@
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C78" s="28" t="s">
+    <row r="78" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C78" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D78" s="28" t="s">
+      <c r="D78" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E78" s="28" t="s">
+      <c r="E78" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F78" s="27"/>
-    </row>
-    <row r="79" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C79" s="28">
+    </row>
+    <row r="79" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C79" s="27">
         <v>7</v>
       </c>
-      <c r="D79" s="28" t="s">
+      <c r="D79" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="E79" s="28" t="s">
+      <c r="E79" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="F79" s="27"/>
-    </row>
-    <row r="80" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C80" s="28">
+    </row>
+    <row r="80" spans="3:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="C80" s="27">
         <v>8</v>
       </c>
-      <c r="D80" s="28" t="s">
+      <c r="D80" s="27" t="s">
         <v>63</v>
       </c>
       <c r="E80" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F80" s="27"/>
-    </row>
-    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="27"/>
-    </row>
-    <row r="84" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+    </row>
+    <row r="84" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
         <v>56</v>
       </c>
@@ -1763,7 +1764,7 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C85" s="17" t="s">
         <v>25</v>
       </c>
@@ -1774,7 +1775,7 @@
       <c r="H85" s="18"/>
       <c r="I85" s="19"/>
     </row>
-    <row r="86" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C86" s="20">
         <v>101</v>
       </c>
@@ -1797,7 +1798,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="87" spans="3:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C87" s="20">
         <v>102</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="88" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C88" s="22">
         <v>103</v>
       </c>

--- a/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
+++ b/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccifu\OneDrive\Escritorio\AXXION_SYSTEM\_docs\trim_03\Normalización Modelo Relacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB465C5D-3106-427A-B34E-1FAA9117AC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735BFB40-14B4-4EC4-972A-2988540CD0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4F9FFE5D-8DC2-4520-A7DA-75C0721EFB2B}"/>
   </bookViews>

--- a/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
+++ b/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccifu\OneDrive\Escritorio\AXXION_SYSTEM\_docs\trim_03\Normalización Modelo Relacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735BFB40-14B4-4EC4-972A-2988540CD0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BC7E40-3801-43CA-A767-EDA5E7981037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4F9FFE5D-8DC2-4520-A7DA-75C0721EFB2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="81">
   <si>
     <t>renta_id</t>
   </si>
@@ -107,9 +107,6 @@
     <t>600.00</t>
   </si>
   <si>
-    <t>Sofía M.</t>
-  </si>
-  <si>
     <t>| cliente_id | nombre | email | telefono |</t>
   </si>
   <si>
@@ -267,6 +264,21 @@
   </si>
   <si>
     <t>2. Ninguna columna que no sea clave debe depender de otra columna que tampoco es clave. (Esto se llama eliminar "dependencias transitivas").</t>
+  </si>
+  <si>
+    <t>usuario_apellido</t>
+  </si>
+  <si>
+    <t>Rodriguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofía </t>
+  </si>
+  <si>
+    <t>Martinez</t>
   </si>
 </sst>
 </file>
@@ -910,41 +922,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D31449-B9E3-460C-85DA-C946E15A5F7C}">
-  <dimension ref="C3:L88"/>
+  <dimension ref="C3:N88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" customWidth="1"/>
     <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C3" s="28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C6" s="28"/>
+    </row>
+    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="28"/>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -956,7 +969,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="3:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C11" s="4" t="s">
         <v>0</v>
       </c>
@@ -984,11 +997,17 @@
       <c r="K11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="3:12" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="N11" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="3:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C12" s="7">
         <v>101</v>
       </c>
@@ -1014,13 +1033,19 @@
         <v>14</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="3:12" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="N12" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C13" s="7">
         <v>102</v>
       </c>
@@ -1046,13 +1071,19 @@
         <v>21</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="3:12" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N13" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="3:14" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="12">
         <v>103</v>
       </c>
@@ -1078,35 +1109,41 @@
         <v>14</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C20" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C24" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1114,16 +1151,16 @@
     </row>
     <row r="28" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="29" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -1131,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>12</v>
@@ -1145,7 +1182,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>12</v>
@@ -1162,7 +1199,7 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31" s="2">
         <v>5588776655</v>
@@ -1170,7 +1207,7 @@
     </row>
     <row r="33" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1182,16 +1219,16 @@
     </row>
     <row r="34" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="F34" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -1203,13 +1240,13 @@
         <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>37</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1221,13 +1258,13 @@
         <v>52</v>
       </c>
       <c r="D36" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="24" t="s">
         <v>38</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>39</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -1246,7 +1283,7 @@
     </row>
     <row r="38" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1258,16 +1295,16 @@
     </row>
     <row r="39" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C39" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -1282,10 +1319,10 @@
         <v>15</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1297,13 +1334,13 @@
         <v>902</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -1315,13 +1352,13 @@
         <v>903</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -1340,7 +1377,7 @@
     </row>
     <row r="44" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -1352,7 +1389,7 @@
     </row>
     <row r="45" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C45" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18"/>
@@ -1466,12 +1503,12 @@
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C52" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
@@ -1479,17 +1516,17 @@
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C59" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1497,16 +1534,16 @@
     </row>
     <row r="60" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C60" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="61" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -1514,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>12</v>
@@ -1528,7 +1565,7 @@
         <v>2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>12</v>
@@ -1545,7 +1582,7 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F63" s="2">
         <v>5588776655</v>
@@ -1553,7 +1590,7 @@
     </row>
     <row r="65" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -1564,16 +1601,16 @@
     </row>
     <row r="66" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C66" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E66" s="18" t="s">
+      <c r="F66" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -1584,13 +1621,13 @@
         <v>51</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="F67" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>37</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -1601,13 +1638,13 @@
         <v>52</v>
       </c>
       <c r="D68" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F68" s="24" t="s">
         <v>38</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F68" s="24" t="s">
-        <v>39</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -1624,7 +1661,7 @@
     </row>
     <row r="70" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -1635,16 +1672,16 @@
     </row>
     <row r="71" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C71" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -1658,10 +1695,10 @@
         <v>15</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -1672,13 +1709,13 @@
         <v>902</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E73" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -1689,13 +1726,13 @@
         <v>903</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -1712,18 +1749,18 @@
     </row>
     <row r="76" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C78" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D78" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="27" t="s">
         <v>59</v>
-      </c>
-      <c r="D78" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E78" s="27" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="79" spans="3:9" x14ac:dyDescent="0.3">
@@ -1731,10 +1768,10 @@
         <v>7</v>
       </c>
       <c r="D79" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" s="30" t="s">
         <v>61</v>
-      </c>
-      <c r="E79" s="30" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="80" spans="3:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1742,10 +1779,10 @@
         <v>8</v>
       </c>
       <c r="D80" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E80" s="29" t="s">
         <v>63</v>
-      </c>
-      <c r="E80" s="29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="81" spans="3:9" x14ac:dyDescent="0.3">
@@ -1755,7 +1792,7 @@
     </row>
     <row r="84" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -1766,7 +1803,7 @@
     </row>
     <row r="85" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C85" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" s="18"/>
       <c r="E85" s="18"/>

--- a/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
+++ b/_docs/trim_03/Normalización Modelo Relacional/NORMALIZACION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccifu\OneDrive\Escritorio\AXXION_SYSTEM\_docs\trim_03\Normalización Modelo Relacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BC7E40-3801-43CA-A767-EDA5E7981037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D1EB72-9D8F-4A4D-AB7B-3170B9318766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4F9FFE5D-8DC2-4520-A7DA-75C0721EFB2B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="89">
   <si>
     <t>renta_id</t>
   </si>
@@ -71,9 +71,6 @@
     <t>500.00</t>
   </si>
   <si>
-    <t>Ana Torres</t>
-  </si>
-  <si>
     <t>ana.t@email.com</t>
   </si>
   <si>
@@ -83,18 +80,12 @@
     <t>SN-112233</t>
   </si>
   <si>
-    <t>Carlos R.</t>
-  </si>
-  <si>
     <t>Vendedor</t>
   </si>
   <si>
     <t>150.00</t>
   </si>
   <si>
-    <t>Luis Pardo</t>
-  </si>
-  <si>
     <t>luis.p@email.com</t>
   </si>
   <si>
@@ -107,12 +98,6 @@
     <t>600.00</t>
   </si>
   <si>
-    <t>| cliente_id | nombre | email | telefono |</t>
-  </si>
-  <si>
-    <t>| renta_id | fecha_inicio | fecha_fin | monto_total | cliente_id | equipo_id | usuario_id |</t>
-  </si>
-  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -122,9 +107,6 @@
     <t>telefono</t>
   </si>
   <si>
-    <t>ana torres</t>
-  </si>
-  <si>
     <t>luis.p@email.com </t>
   </si>
   <si>
@@ -158,9 +140,6 @@
     <t xml:space="preserve"> SN-445566</t>
   </si>
   <si>
-    <t>nombre_completo</t>
-  </si>
-  <si>
     <t>rol</t>
   </si>
   <si>
@@ -176,15 +155,9 @@
     <t>Clientes</t>
   </si>
   <si>
-    <t xml:space="preserve"> Pedro G.</t>
-  </si>
-  <si>
     <t> pedro@empresa.com </t>
   </si>
   <si>
-    <t xml:space="preserve"> Sofía M.</t>
-  </si>
-  <si>
     <t>carlos@empresa.com</t>
   </si>
   <si>
@@ -206,27 +179,15 @@
     <t>Rentas</t>
   </si>
   <si>
-    <t>rolId</t>
-  </si>
-  <si>
     <t>Roles</t>
   </si>
   <si>
-    <t>idrol</t>
-  </si>
-  <si>
     <t xml:space="preserve">descripcion </t>
   </si>
   <si>
-    <t>saul M,</t>
-  </si>
-  <si>
     <t>administra los usuarios</t>
   </si>
   <si>
-    <t>sofia P.</t>
-  </si>
-  <si>
     <t>Realiza mantenimientos a los equipos</t>
   </si>
   <si>
@@ -279,13 +240,76 @@
   </si>
   <si>
     <t>Martinez</t>
+  </si>
+  <si>
+    <t>cliente_apellido</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis </t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sofía </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pedro</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fecha_inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecha_fin </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> monto_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente_id </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> equipo_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">usuario_id </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> renta_id  </t>
+  </si>
+  <si>
+    <t>id_rol</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saul </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cliente_id </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,12 +324,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -525,67 +543,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -926,20 +947,27 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C3" s="28" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="3:14" x14ac:dyDescent="0.3">
@@ -947,17 +975,17 @@
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="3:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -986,22 +1014,22 @@
         <v>4</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="J11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="L11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>9</v>
+      <c r="M11" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>9</v>
@@ -1021,28 +1049,28 @@
         <v>10</v>
       </c>
       <c r="G12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="J12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="K12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="L12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="3:14" ht="31.2" x14ac:dyDescent="0.3">
@@ -1056,31 +1084,31 @@
         <v>45141</v>
       </c>
       <c r="F13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="K13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="L13" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>16</v>
+        <v>65</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="3:14" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1094,120 +1122,132 @@
         <v>45147</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="J14" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="K14" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="L14" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="N14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C20" s="28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C24" s="28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C28" s="2" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="2">
+        <v>71</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="2">
         <v>55511223344</v>
       </c>
     </row>
-    <row r="30" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C30" s="2">
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="2">
+        <v>71</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="2">
         <v>55511223345</v>
       </c>
     </row>
-    <row r="31" spans="3:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C31" s="2">
         <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="2">
+        <v>70</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="2">
         <v>5588776655</v>
       </c>
     </row>
     <row r="33" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1219,16 +1259,16 @@
     </row>
     <row r="34" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -1240,13 +1280,13 @@
         <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1258,13 +1298,13 @@
         <v>52</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -1283,7 +1323,7 @@
     </row>
     <row r="38" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C38" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1295,18 +1335,20 @@
     </row>
     <row r="39" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C39" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -1316,15 +1358,17 @@
         <v>901</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G40" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -1334,15 +1378,17 @@
         <v>902</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -1352,15 +1398,17 @@
         <v>903</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -1377,7 +1425,7 @@
     </row>
     <row r="44" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -1389,14 +1437,26 @@
     </row>
     <row r="45" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C45" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I45" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -1503,12 +1563,12 @@
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C52" s="28" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
@@ -1516,17 +1576,17 @@
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="28" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C59" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1534,16 +1594,19 @@
     </row>
     <row r="60" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C60" s="2" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -1551,12 +1614,15 @@
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="2">
+        <v>71</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="2">
         <v>55511223344</v>
       </c>
     </row>
@@ -1565,12 +1631,15 @@
         <v>2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="2">
+        <v>71</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="2">
         <v>55511223345</v>
       </c>
     </row>
@@ -1579,18 +1648,21 @@
         <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F63" s="2">
+        <v>70</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="2">
         <v>5588776655</v>
       </c>
     </row>
     <row r="65" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -1601,16 +1673,16 @@
     </row>
     <row r="66" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C66" s="17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -1621,13 +1693,13 @@
         <v>51</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -1638,13 +1710,13 @@
         <v>52</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -1661,7 +1733,7 @@
     </row>
     <row r="70" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -1672,18 +1744,20 @@
     </row>
     <row r="71" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C71" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
@@ -1692,15 +1766,17 @@
         <v>901</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G72" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
@@ -1709,15 +1785,17 @@
         <v>902</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G73" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
@@ -1726,15 +1804,17 @@
         <v>903</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
@@ -1749,50 +1829,63 @@
     </row>
     <row r="76" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="78" spans="3:9" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C78" s="27" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="79" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C79" s="27">
+        <v>73</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G78" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C79" s="29">
         <v>7</v>
       </c>
-      <c r="D79" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E79" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="3:9" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="C80" s="27">
+      <c r="D79" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="3:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C80" s="29">
         <v>8</v>
       </c>
-      <c r="D80" s="27" t="s">
-        <v>62</v>
+      <c r="D80" s="29" t="s">
+        <v>86</v>
       </c>
       <c r="E80" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
+        <v>85</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="84" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -1803,14 +1896,26 @@
     </row>
     <row r="85" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C85" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="18"/>
-      <c r="H85" s="18"/>
-      <c r="I85" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I85" s="19" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="86" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C86" s="20">
@@ -1883,13 +1988,13 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H12" r:id="rId1" display="https://www.google.com/url?sa=E&amp;q=mailto%3Aana.t%40email.com" xr:uid="{AFC349DD-60A1-485A-A681-3C6D5471D351}"/>
-    <hyperlink ref="H13" r:id="rId2" display="https://www.google.com/url?sa=E&amp;q=mailto%3Aluis.p%40email.com" xr:uid="{2B5CE3F7-3CFC-40D2-AA09-71D66D7045B0}"/>
-    <hyperlink ref="H14" r:id="rId3" display="https://www.google.com/url?sa=E&amp;q=mailto%3Aana.t%40email.com" xr:uid="{8D9AC21E-425B-4054-A49C-115376EF2650}"/>
-    <hyperlink ref="E29" r:id="rId4" xr:uid="{83F5EF3F-E992-49DB-B722-5BFD52E42658}"/>
-    <hyperlink ref="E30" r:id="rId5" xr:uid="{3731C535-D9A3-4358-BC9C-74E4D04983F4}"/>
-    <hyperlink ref="E61" r:id="rId6" xr:uid="{6AC75017-10EA-4622-AB8D-B0B2879EC7CD}"/>
-    <hyperlink ref="E62" r:id="rId7" xr:uid="{1F3693C7-14C2-47A6-AA76-4114D61831B7}"/>
+    <hyperlink ref="I12" r:id="rId1" display="https://www.google.com/url?sa=E&amp;q=mailto%3Aana.t%40email.com" xr:uid="{EF9819CD-EA46-40E3-814D-E1EF63B573E9}"/>
+    <hyperlink ref="I13" r:id="rId2" display="https://www.google.com/url?sa=E&amp;q=mailto%3Aluis.p%40email.com" xr:uid="{CF078B1A-67E2-40BA-BB2D-A21CD34F9DAC}"/>
+    <hyperlink ref="I14" r:id="rId3" display="https://www.google.com/url?sa=E&amp;q=mailto%3Aana.t%40email.com" xr:uid="{A51F0BDA-F7F6-4C82-9C97-1461249E5013}"/>
+    <hyperlink ref="F29" r:id="rId4" xr:uid="{DC0D7083-BE3E-4000-98B5-4A1AE96E2CDE}"/>
+    <hyperlink ref="F30" r:id="rId5" xr:uid="{FC916874-7DAF-4122-B31A-C6B0213B1E1C}"/>
+    <hyperlink ref="F61" r:id="rId6" xr:uid="{88181BB0-162C-4B14-B56A-E01990A03B94}"/>
+    <hyperlink ref="F62" r:id="rId7" xr:uid="{8ABBD61C-CA91-47ED-8F8A-59A35AED0320}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId8"/>
